--- a/artfynd/A 8386-2026 artfynd.xlsx
+++ b/artfynd/A 8386-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130794741</v>
       </c>
       <c r="B2" t="n">
-        <v>93121</v>
+        <v>93223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130794740</v>
       </c>
       <c r="B3" t="n">
-        <v>98930</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
